--- a/examples/PL-template-coach.xlsx
+++ b/examples/PL-template-coach.xlsx
@@ -20,6 +20,20 @@
     <author>Author</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>Riga con A vuota = nuovo blocco: nome in B, varianti sotto le alzate.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>Date della settimana (testo libero, facoltativo).</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="C1" authorId="0">
       <text>
         <r>
@@ -82,7 +96,7 @@
     <t>• La prima nota di un giorno diventa il suo banner nell'app.</t>
   </si>
   <si>
-    <t>• overall (facoltativo): week | giorno (date) | tipo | colonne delle alzate. Una riga con A vuota apre un blocco: nome in B, varianti sotto le alzate.</t>
+    <t>• overall (facoltativo): week | giorno (date) | tipo | colonne delle alzate, come nel formato PL28. Una riga con A vuota apre un blocco: nome in B, varianti sotto le alzate. Due righe vuote di fila chiudono il foglio.</t>
   </si>
   <si>
     <t>• Tipo di settimana (menu a tendina): normale (o vuoto), scarico, transizione, ramping, intensificazione, picco, taper, entrata, test, gara. In questo formato il tipo non cambia le serie.</t>
@@ -751,7 +765,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="7" width="24" customWidth="1"/>
   </cols>
@@ -1080,7 +1094,7 @@
         <v>56</v>
       </c>
       <c r="B1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/examples/PL-template-coach.xlsx
+++ b/examples/PL-template-coach.xlsx
@@ -48,6 +48,13 @@
         </r>
       </text>
     </comment>
+    <comment ref="A2" authorId="0">
+      <text>
+        <r>
+          <t>Tipo di ogni alzata (facoltativo, testo libero): stressante, rigenerante, tecnica… L'app lo mostra accanto al nome.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -70,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="60">
   <si>
     <t>Template PL – formato coach (ogni sessione scritta per intero)</t>
   </si>
@@ -96,7 +103,7 @@
     <t>• La prima nota di un giorno diventa il suo banner nell'app.</t>
   </si>
   <si>
-    <t>• overall (facoltativo): week | giorno (date) | tipo | colonne delle alzate, come nel formato PL28. Una riga con A vuota apre un blocco: nome in B, varianti sotto le alzate. Due righe vuote di fila chiudono il foglio.</t>
+    <t>• overall (facoltativo): week | giorno (date) | tipo | colonne delle alzate, come nel formato PL28. Riga 2 facoltativa "tipo alzata": il tipo di ogni colonna (stressante, rigenerante…) vale per le righe del training log che puntano a quella colonna. Una riga con A vuota apre un blocco: nome in B, varianti sotto le alzate. Due righe vuote di fila chiudono il foglio.</t>
   </si>
   <si>
     <t>• Tipo di settimana (menu a tendina): normale (o vuoto), scarico, transizione, ramping, intensificazione, picco, taper, entrata, test, gara. In questo formato il tipo non cambia le serie.</t>
@@ -138,10 +145,19 @@
     <t>Panca (A)</t>
   </si>
   <si>
+    <t>Panca var. (C)</t>
+  </si>
+  <si>
     <t>Stacco (B)</t>
   </si>
   <si>
-    <t>Panca var. (C)</t>
+    <t>tipo alzata</t>
+  </si>
+  <si>
+    <t>stressante</t>
+  </si>
+  <si>
+    <t>rigenerante</t>
   </si>
   <si>
     <t>Blocco 1 – ESEMPIO</t>
@@ -761,10 +777,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="7" width="24" customWidth="1"/>
@@ -794,50 +810,72 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="str">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="str">
         <f>"4x5 "&amp;MROUND(Massimali!$B$3*0.75,2.5)&amp;"kg"</f>
         <v>4x5 135kg</v>
       </c>
-      <c r="E3" s="2" t="str">
+      <c r="E4" s="2" t="str">
         <f>"5x5 "&amp;MROUND(Massimali!$B$4*0.72,2.5)&amp;"kg"</f>
         <v>5x5 87,5kg</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="2" t="str">
+      <c r="F4" s="2" t="str">
         <f>MROUND(Massimali!$B$4*0.65,2.5)&amp;"kg 30-35RT"</f>
         <v>77,5kg 30-35RT</v>
       </c>
+      <c r="G4" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Valore non ammesso" error="Usa uno di: normale, scarico, transizione, ramping, intensificazione, picco, taper, entrata, test, gara" sqref="C2:C400">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Valore non ammesso" error="Usa uno di: normale, scarico, transizione, ramping, intensificazione, picco, taper, entrata, test, gara" sqref="C3:C400">
       <formula1>"normale,scarico,transizione,ramping,intensificazione,picco,taper,entrata,test,gara"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorStyle="stop" errorTitle="Valore non ammesso" error="Usa uno di: stressante, rigenerante, tecnica, stimolo, volume" sqref="D2:G2">
+      <formula1>"stressante,rigenerante,tecnica,stimolo,volume"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -864,34 +902,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -899,16 +937,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f>overall!D3</f>
+        <f>overall!D4</f>
         <v>4x5 135kg</v>
       </c>
       <c r="F2" s="2"/>
@@ -916,7 +954,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -924,16 +962,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E3" s="2" t="str">
-        <f>overall!E3</f>
+        <f>overall!E4</f>
         <v>5x5 87,5kg</v>
       </c>
       <c r="F3" s="2"/>
@@ -941,7 +979,7 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -949,25 +987,25 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -975,16 +1013,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="str">
-        <f>overall!F3</f>
+        <f>overall!G4</f>
         <v>4@7 + 90% 3x4</v>
       </c>
       <c r="F6" s="2"/>
@@ -992,7 +1030,7 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -1000,23 +1038,23 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1024,16 +1062,16 @@
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="str">
-        <f>overall!G3</f>
+        <f>overall!F4</f>
         <v>77,5kg 30-35RT</v>
       </c>
       <c r="F9" s="2"/>
@@ -1041,7 +1079,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1049,23 +1087,23 @@
         <v>1</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1091,7 +1129,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B1">
         <v>2</v>
